--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486490_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486490_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0815</v>
+        <v>4.3582</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5566</v>
+        <v>3.4326</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5249</v>
+        <v>0.9256</v>
       </c>
       <c r="G2" t="n">
         <v>-1.1734</v>
@@ -610,13 +610,13 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0703</v>
+        <v>0.2064</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7413999999999999</v>
+        <v>0.1346</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3289</v>
+        <v>0.0718</v>
       </c>
       <c r="V2" t="n">
         <v>3.5851</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3074</v>
+        <v>3.4378</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7514</v>
+        <v>0.3482</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0588</v>
+        <v>3.0896</v>
       </c>
       <c r="G3" t="n">
         <v>-0.6599</v>
@@ -688,13 +688,13 @@
         <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1849</v>
+        <v>0.9454</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9349</v>
+        <v>0.1646</v>
       </c>
       <c r="U3" t="n">
-        <v>0.75</v>
+        <v>0.7808</v>
       </c>
       <c r="V3" t="n">
         <v>2.0647</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8416</v>
+        <v>2.623</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.706</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7629</v>
+        <v>1.917</v>
       </c>
       <c r="G4" t="n">
         <v>0.7883</v>
@@ -766,13 +766,13 @@
         <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2518</v>
+        <v>0.5296</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.548</v>
+        <v>0.0793</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2962</v>
+        <v>0.4503</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. CECCARDI</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0151</v>
+        <v>1.5052</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2265</v>
+        <v>2.5427</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2114</v>
+        <v>-1.0375</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.7165</v>
+        <v>0.2861</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9729</v>
+        <v>-1.2957</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.7435</v>
+        <v>1.5818</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3648</v>
+        <v>2.8203</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0421</v>
+        <v>-0.0333</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3227</v>
+        <v>2.8536</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3517</v>
+        <v>-2.5342</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-1.2624</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4208</v>
+        <v>-1.2718</v>
       </c>
       <c r="P5" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5571</v>
+        <v>0.1316</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0263</v>
+        <v>-0.2776</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5308</v>
+        <v>0.4092</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3045</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>S. RODRIGUEZ FEBLES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8617</v>
+        <v>0.9791</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2074</v>
+        <v>-0.5423</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3457</v>
+        <v>1.5214</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2861</v>
+        <v>-1.9884</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2957</v>
+        <v>0.2404</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5818</v>
+        <v>-2.2288</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8203</v>
+        <v>-1.1157</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0333</v>
+        <v>1.1378</v>
       </c>
       <c r="L6" t="n">
-        <v>2.8536</v>
+        <v>-2.2535</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.5342</v>
+        <v>-0.8727</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2624</v>
+        <v>-0.8974</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2718</v>
+        <v>0.0247</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5119</v>
+        <v>0.6402</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6128</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1009</v>
+        <v>0.6318</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. MC MULLEN</t>
+          <t>S. CECCARDI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5162</v>
+        <v>0.6288</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9558</v>
+        <v>0.6244</v>
       </c>
       <c r="F7" t="n">
-        <v>1.472</v>
+        <v>0.0044</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.8127</v>
+        <v>-2.7165</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.1377</v>
+        <v>-0.9729</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.675</v>
+        <v>-1.7435</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.7265</v>
+        <v>-0.3648</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.3894</v>
+        <v>-0.0421</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3371</v>
+        <v>-0.3227</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0863</v>
+        <v>-2.3517</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7484</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3379</v>
+        <v>-1.4208</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.305</v>
+        <v>0.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>3.9597</v>
+        <v>1.1708</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2508</v>
+        <v>0.4242</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7089</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6743</v>
+        <v>1.3045</v>
       </c>
       <c r="W7" t="n">
-        <v>1.695</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.0207</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="8">
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ FEBLES</t>
+          <t>J. GODSPOWER JOHNSON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4076</v>
+        <v>-0.5844</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.083</v>
+        <v>-1.5341</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4906</v>
+        <v>0.9497</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9884</v>
+        <v>-3.0695</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2404</v>
+        <v>-0.1825</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.2288</v>
+        <v>-2.887</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1157</v>
+        <v>-1.5498</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1378</v>
+        <v>0.5324</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.2535</v>
+        <v>-2.0822</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8727</v>
+        <v>-1.5197</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8974</v>
+        <v>-0.7149</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0247</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.9626</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5323</v>
+        <v>0.0156</v>
       </c>
       <c r="U9" t="n">
-        <v>0.601</v>
+        <v>0.9469</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. GODSPOWER JOHNSON</t>
+          <t>I. CRUZ UCEDA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2325</v>
+        <v>-0.7418</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0871</v>
+        <v>1.1081</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3196</v>
+        <v>-1.8499</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.0695</v>
+        <v>-3.091</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1825</v>
+        <v>-2.8312</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.887</v>
+        <v>-0.2598</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5498</v>
+        <v>-0.2923</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5324</v>
+        <v>-1.9003</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.0822</v>
+        <v>1.6081</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5197</v>
+        <v>-2.7987</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7149</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-1.8679</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>1.7795</v>
+        <v>0.9142</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4627</v>
+        <v>0.2704</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3168</v>
+        <v>0.6438</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. CRUZ UCEDA</t>
+          <t>N. MC MULLEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0414</v>
+        <v>-1.205</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0454</v>
+        <v>-2.0914</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.004</v>
+        <v>0.8864</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.091</v>
+        <v>-3.8127</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.8312</v>
+        <v>-2.1377</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2598</v>
+        <v>-1.675</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2923</v>
+        <v>-2.7265</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.9003</v>
+        <v>-1.3894</v>
       </c>
       <c r="L11" t="n">
-        <v>1.6081</v>
+        <v>-1.3371</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.7987</v>
+        <v>-1.0863</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.7484</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.8679</v>
+        <v>-0.3379</v>
       </c>
       <c r="P11" t="n">
-        <v>0.87</v>
+        <v>-1.305</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R11" t="n">
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6974</v>
+        <v>2.2385</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2077</v>
+        <v>1.1152</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4897</v>
+        <v>1.1233</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.6743</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.695</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.0207</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6747</v>
+        <v>-4.3432</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6849</v>
+        <v>-2.0143</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9898</v>
+        <v>-2.3289</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5735</v>
@@ -1390,13 +1390,13 @@
         <v>0.435</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0566</v>
+        <v>0.2749</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0959</v>
+        <v>-0.4254</v>
       </c>
       <c r="U12" t="n">
-        <v>1.0393</v>
+        <v>0.7003</v>
       </c>
       <c r="V12" t="n">
         <v>-1.3045</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.1188</v>
+        <v>7.146200000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.570900000000001</v>
+        <v>3.598399999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>3.547900000000001</v>
+        <v>3.547800000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-16.236</v>
@@ -1438,28 +1438,28 @@
         <v>-11.3431</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.892700000000001</v>
+        <v>-4.8927</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9586</v>
+        <v>-0.9586000000000002</v>
       </c>
       <c r="K13" t="n">
         <v>-2.202</v>
       </c>
       <c r="L13" t="n">
-        <v>1.243300000000001</v>
+        <v>1.2433</v>
       </c>
       <c r="M13" t="n">
         <v>-15.2773</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.141499999999999</v>
+        <v>-9.141500000000001</v>
       </c>
       <c r="O13" t="n">
         <v>-6.136100000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>7.612599999999999</v>
+        <v>7.6126</v>
       </c>
       <c r="Q13" t="n">
         <v>-5.4377</v>
@@ -1468,10 +1468,10 @@
         <v>13.0503</v>
       </c>
       <c r="S13" t="n">
-        <v>6.483299999999999</v>
+        <v>7.5107</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2766999999999997</v>
+        <v>1.3038</v>
       </c>
       <c r="U13" t="n">
         <v>6.2067</v>
@@ -1480,10 +1480,10 @@
         <v>8.258900000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>8.690800000000001</v>
+        <v>8.690799999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.4318999999999997</v>
+        <v>-0.4318999999999998</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.836</v>
+        <v>9.012600000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>6.4249</v>
+        <v>6.8719</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4111</v>
+        <v>2.1406</v>
       </c>
       <c r="G14" t="n">
         <v>10.1684</v>
@@ -1546,13 +1546,13 @@
         <v>0.87</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0725</v>
+        <v>-0.8959</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5069</v>
+        <v>-1.0599</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5655</v>
+        <v>0.164</v>
       </c>
       <c r="V14" t="n">
         <v>-1.13</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4818</v>
+        <v>3.5236</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1522</v>
+        <v>2.4816</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3296</v>
+        <v>1.042</v>
       </c>
       <c r="G15" t="n">
         <v>6.8619</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7944</v>
+        <v>-0.1637</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0517</v>
+        <v>-0.6189</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7427</v>
+        <v>0.4551</v>
       </c>
       <c r="V15" t="n">
         <v>-1.8695</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6661</v>
+        <v>0.787</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0485</v>
+        <v>0.175</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7146</v>
+        <v>0.612</v>
       </c>
       <c r="G16" t="n">
         <v>2.346</v>
@@ -1702,13 +1702,13 @@
         <v>0.435</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8103</v>
+        <v>-0.6895</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4384</v>
+        <v>-1.2149</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6281</v>
+        <v>0.5254</v>
       </c>
       <c r="V16" t="n">
         <v>-1.3045</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1769</v>
+        <v>0.629</v>
       </c>
       <c r="E17" t="n">
         <v>-0.8411999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0181</v>
+        <v>1.4702</v>
       </c>
       <c r="G17" t="n">
         <v>3.6996</v>
@@ -1780,13 +1780,13 @@
         <v>0.435</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2384</v>
+        <v>-0.7862</v>
       </c>
       <c r="T17" t="n">
         <v>-0.7619</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4765</v>
+        <v>-0.0244</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5443</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7399</v>
+        <v>-1.7091</v>
       </c>
       <c r="E18" t="n">
         <v>-0.032</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7079</v>
+        <v>-1.6771</v>
       </c>
       <c r="G18" t="n">
         <v>-0.413</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.197</v>
+        <v>-0.1661</v>
       </c>
       <c r="T18" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>-1.13</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2962</v>
+        <v>-2.3077</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9945000000000001</v>
+        <v>-0.8828</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3016</v>
+        <v>-1.4249</v>
       </c>
       <c r="G19" t="n">
         <v>-2.065</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2312</v>
+        <v>-0.2427</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3425</v>
+        <v>-0.2307</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1113</v>
+        <v>-0.012</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0241</v>
+        <v>-2.6708</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.614</v>
+        <v>-2.5022</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4101</v>
+        <v>-0.1686</v>
       </c>
       <c r="G20" t="n">
         <v>0.4495</v>
@@ -2014,13 +2014,13 @@
         <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.211</v>
+        <v>-0.8577</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0274</v>
+        <v>-0.9157</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1835</v>
+        <v>0.058</v>
       </c>
       <c r="V20" t="n">
         <v>0.5649999999999999</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.318</v>
+        <v>-3.2949</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2029</v>
+        <v>-2.4264</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1151</v>
+        <v>-0.8685</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4482</v>
@@ -2092,13 +2092,13 @@
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3271</v>
+        <v>-0.304</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0769</v>
+        <v>-0.3004</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2502</v>
+        <v>-0.0036</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3252</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8344</v>
+        <v>-3.6122</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6205</v>
+        <v>-2.7322</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2139</v>
+        <v>-0.8799</v>
       </c>
       <c r="G22" t="n">
         <v>0.6334</v>
@@ -2170,13 +2170,13 @@
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5977</v>
+        <v>-0.3755</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4194</v>
+        <v>-0.5311</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1783</v>
+        <v>0.1556</v>
       </c>
       <c r="V22" t="n">
         <v>-1.695</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0673</v>
+        <v>-4.9864</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7714</v>
+        <v>-3.6597</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2959</v>
+        <v>-1.3267</v>
       </c>
       <c r="G23" t="n">
         <v>-3.9968</v>
@@ -2248,13 +2248,13 @@
         <v>0.435</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5926</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6165</v>
+        <v>-0.5047</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0239</v>
+        <v>-0.0069</v>
       </c>
       <c r="V23" t="n">
         <v>0.1745</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1191</v>
+        <v>-4.628899999999998</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.5479</v>
+        <v>-3.548</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.5711</v>
+        <v>-1.080900000000002</v>
       </c>
       <c r="G24" t="n">
         <v>16.2358</v>
@@ -2326,13 +2326,13 @@
         <v>5.437499999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.4834</v>
+        <v>-4.992900000000001</v>
       </c>
       <c r="T24" t="n">
         <v>-6.2067</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2764999999999999</v>
+        <v>1.2136</v>
       </c>
       <c r="V24" t="n">
         <v>-8.259</v>
